--- a/submissions/10-carton-bid-evaluation/inputs/bid_receipt_log_itb_2026_17.xlsx
+++ b/submissions/10-carton-bid-evaluation/inputs/bid_receipt_log_itb_2026_17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4422657-1949-2A41-94CB-F9E2DEF875D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F96DB4-965D-2B40-A8D5-E5034273FDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="103">
   <si>
     <t>Purchasing office receipt log, Nordvik Manufacturing, Alexandria; items received or handed out on open solicitations, October 1 through October 12, 2026</t>
   </si>
@@ -230,13 +230,16 @@
     <t>R-1056</t>
   </si>
   <si>
-    <t>09:35</t>
+    <t>09:38</t>
+  </si>
+  <si>
+    <t>C. Hennen</t>
   </si>
   <si>
     <t>Telephone</t>
   </si>
   <si>
-    <t>Message taken: item 3 to be read at 0.255</t>
+    <t>Message taken: item 1 to be read at 0.594</t>
   </si>
   <si>
     <t>R-1057</t>
@@ -1219,13 +1222,13 @@
         <v>71</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -1237,16 +1240,16 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>13</v>
@@ -1264,16 +1267,16 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>46</v>
@@ -1291,13 +1294,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>27</v>
@@ -1318,22 +1321,22 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>62</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -1345,22 +1348,22 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -1372,22 +1375,22 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
@@ -1399,22 +1402,22 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
@@ -1437,7 +1440,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>

--- a/submissions/10-carton-bid-evaluation/inputs/bid_receipt_log_itb_2026_17.xlsx
+++ b/submissions/10-carton-bid-evaluation/inputs/bid_receipt_log_itb_2026_17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F96DB4-965D-2B40-A8D5-E5034273FDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E42D08-0F7A-8B40-A07F-3A6E75C1EC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="102">
   <si>
     <t>Purchasing office receipt log, Nordvik Manufacturing, Alexandria; items received or handed out on open solicitations, October 1 through October 12, 2026</t>
   </si>
@@ -71,6 +71,21 @@
     <t>R-1040</t>
   </si>
   <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>Dahlgren Box, St. Cloud</t>
+  </si>
+  <si>
+    <t>Own truck</t>
+  </si>
+  <si>
+    <t>Sealed bid envelope; samples, 5 cartons</t>
+  </si>
+  <si>
+    <t>R-1041</t>
+  </si>
+  <si>
     <t>10/02/2026</t>
   </si>
   <si>
@@ -83,34 +98,34 @@
     <t>JL</t>
   </si>
   <si>
-    <t>R-1041</t>
+    <t>R-1042</t>
   </si>
   <si>
     <t>10:26</t>
   </si>
   <si>
+    <t>Pemberton, Neenah</t>
+  </si>
+  <si>
+    <t>R-1043</t>
+  </si>
+  <si>
+    <t>11:14</t>
+  </si>
+  <si>
+    <t>Loken &amp; Vik</t>
+  </si>
+  <si>
+    <t>R-1044</t>
+  </si>
+  <si>
+    <t>13:48</t>
+  </si>
+  <si>
     <t>Ridgecrest Pkg, Cedar Rapids</t>
   </si>
   <si>
-    <t>R-1042</t>
-  </si>
-  <si>
-    <t>11:14</t>
-  </si>
-  <si>
-    <t>Loken &amp; Vik</t>
-  </si>
-  <si>
-    <t>Own truck</t>
-  </si>
-  <si>
-    <t>R-1043</t>
-  </si>
-  <si>
-    <t>13:48</t>
-  </si>
-  <si>
-    <t>R-1044</t>
+    <t>R-1045</t>
   </si>
   <si>
     <t>14:31</t>
@@ -119,7 +134,7 @@
     <t>Brannock Box</t>
   </si>
   <si>
-    <t>R-1045</t>
+    <t>R-1046</t>
   </si>
   <si>
     <t>10/05/2026</t>
@@ -128,10 +143,7 @@
     <t>09:06</t>
   </si>
   <si>
-    <t>Pemberton, Neenah</t>
-  </si>
-  <si>
-    <t>R-1046</t>
+    <t>R-1047</t>
   </si>
   <si>
     <t>10:15</t>
@@ -140,25 +152,19 @@
     <t>Mesabi Container, Duluth</t>
   </si>
   <si>
-    <t>R-1047</t>
-  </si>
-  <si>
-    <t>11:37</t>
-  </si>
-  <si>
     <t>R-1048</t>
   </si>
   <si>
     <t>15:52</t>
   </si>
   <si>
-    <t>A. Delaney</t>
+    <t>C. Hennen</t>
   </si>
   <si>
     <t>In person</t>
   </si>
   <si>
-    <t>Letter; envelope R-1041 handed back unopened</t>
+    <t>Letter; envelope R-1040 handed back unopened</t>
   </si>
   <si>
     <t>R-1049</t>
@@ -185,9 +191,6 @@
     <t>Otter Tail Corr.</t>
   </si>
   <si>
-    <t>Sealed bid envelope; samples, 5 cartons</t>
-  </si>
-  <si>
     <t>R-1052</t>
   </si>
   <si>
@@ -221,34 +224,28 @@
     <t>R-1055</t>
   </si>
   <si>
-    <t>09:33</t>
-  </si>
-  <si>
-    <t>Dahlgren Box, St. Cloud</t>
+    <t>09:41</t>
+  </si>
+  <si>
+    <t>W &amp; K Corrugated, La Crosse</t>
   </si>
   <si>
     <t>R-1056</t>
   </si>
   <si>
-    <t>09:38</t>
-  </si>
-  <si>
-    <t>C. Hennen</t>
+    <t>09:52</t>
+  </si>
+  <si>
+    <t>R-1057</t>
+  </si>
+  <si>
+    <t>09:56</t>
   </si>
   <si>
     <t>Telephone</t>
   </si>
   <si>
-    <t>Message taken: item 1 to be read at 0.594</t>
-  </si>
-  <si>
-    <t>R-1057</t>
-  </si>
-  <si>
-    <t>09:41</t>
-  </si>
-  <si>
-    <t>W &amp; K Corrugated, La Crosse</t>
+    <t>Message taken: item 1 to be read at 0.548</t>
   </si>
   <si>
     <t>R-1058</t>
@@ -784,25 +781,25 @@
         <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I5" s="2"/>
     </row>
@@ -811,70 +808,70 @@
         <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>14</v>
@@ -883,25 +880,25 @@
         <v>15</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>14</v>
@@ -910,25 +907,25 @@
         <v>15</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>14</v>
@@ -937,22 +934,22 @@
         <v>15</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>13</v>
@@ -964,55 +961,55 @@
         <v>15</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -1024,22 +1021,22 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -1051,157 +1048,157 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="C16" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
@@ -1213,49 +1210,49 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I21" s="2"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -1267,103 +1264,103 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="E23" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I23" s="2"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I24" s="2"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I25" s="2"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -1375,55 +1372,55 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I28" s="2"/>
     </row>
@@ -1440,7 +1437,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
